--- a/Excel – de intermedio a avanzado/documentos/ADJUNTAR 037 (FUNCION BUSCARX).xlsx
+++ b/Excel – de intermedio a avanzado/documentos/ADJUNTAR 037 (FUNCION BUSCARX).xlsx
@@ -5,16 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\michi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\michi\OneDrive\Desktop\Santander-Open-Academy\Excel – de intermedio a avanzado\documentos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8A74305-E60D-4F4A-B985-8164E8E010C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB3414AF-1316-43AF-8CFE-0A8D7C6A5EA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BUSCARX" sheetId="2" r:id="rId1"/>
     <sheet name="BUSCARX2" sheetId="4" r:id="rId2"/>
+    <sheet name="Ejercicio" sheetId="5" r:id="rId3"/>
+    <sheet name="ejercicio 2" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="66">
   <si>
     <t>REFERENCIA</t>
   </si>
@@ -100,6 +102,138 @@
   </si>
   <si>
     <t>H020</t>
+  </si>
+  <si>
+    <t>ALUMNO</t>
+  </si>
+  <si>
+    <t>EVA1</t>
+  </si>
+  <si>
+    <t>EVA2</t>
+  </si>
+  <si>
+    <t>EVA3</t>
+  </si>
+  <si>
+    <t>EVA4</t>
+  </si>
+  <si>
+    <t>MEDIA</t>
+  </si>
+  <si>
+    <t>CALIFICACION</t>
+  </si>
+  <si>
+    <t>AL001</t>
+  </si>
+  <si>
+    <t>AL002</t>
+  </si>
+  <si>
+    <t>AL003</t>
+  </si>
+  <si>
+    <t>AL004</t>
+  </si>
+  <si>
+    <t>AL005</t>
+  </si>
+  <si>
+    <t>AL006</t>
+  </si>
+  <si>
+    <t>AL007</t>
+  </si>
+  <si>
+    <t>AL008</t>
+  </si>
+  <si>
+    <t>NOTA</t>
+  </si>
+  <si>
+    <t>MUY DEFICIENTE</t>
+  </si>
+  <si>
+    <t>INSUFICIENTE</t>
+  </si>
+  <si>
+    <t>SUFICIENTE</t>
+  </si>
+  <si>
+    <t>NOTABLE</t>
+  </si>
+  <si>
+    <t>SOBRESALIENTE</t>
+  </si>
+  <si>
+    <t>GHJK</t>
+  </si>
+  <si>
+    <t>FD</t>
+  </si>
+  <si>
+    <t>ASD</t>
+  </si>
+  <si>
+    <t>DFGH</t>
+  </si>
+  <si>
+    <t>RTYU</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>GRIS</t>
+  </si>
+  <si>
+    <t>MOD-005</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>AMARILLO</t>
+  </si>
+  <si>
+    <t>MOD-004</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>VERDE</t>
+  </si>
+  <si>
+    <t>MOD-003</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>ROJO</t>
+  </si>
+  <si>
+    <t>MOD-002</t>
+  </si>
+  <si>
+    <t>XL</t>
+  </si>
+  <si>
+    <t>AZUL</t>
+  </si>
+  <si>
+    <t>MOD-001</t>
+  </si>
+  <si>
+    <t>TALLA</t>
+  </si>
+  <si>
+    <t>COLOR</t>
+  </si>
+  <si>
+    <t>CODIGO</t>
   </si>
 </sst>
 </file>
@@ -169,7 +303,27 @@
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -180,6 +334,19 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C22CECE2-DFF7-4208-B12B-63954BF50F69}" name="T_CODIGOS" displayName="T_CODIGOS" ref="E1:H6" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="E1:H6" xr:uid="{F8DEF0B1-A729-4D14-8E5B-5A35F0DB510B}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{D226A25D-0568-4237-9151-2FD10524505B}" name="CODIGO"/>
+    <tableColumn id="2" xr3:uid="{936DCAA9-AF2A-4B14-9EC2-DE4431F8C1E3}" name="MODELO"/>
+    <tableColumn id="3" xr3:uid="{46BCF270-21FF-403D-856D-FF870497DDA7}" name="COLOR"/>
+    <tableColumn id="4" xr3:uid="{D07D2C1E-E03C-45C6-85D1-8C1051341E93}" name="TALLA"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -913,9 +1080,578 @@
       <c r="A8" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="1"/>
+      <c r="B8" s="1">
+        <f>_xlfn.XLOOKUP(B7,B3:M3,B2:M2,"No encontrada",0)</f>
+        <v>45.25</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2B3BD12-F4AA-460A-ADA3-2F1DFA27F0BF}">
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="11.9296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2">
+        <v>2.5</v>
+      </c>
+      <c r="C2">
+        <v>5</v>
+      </c>
+      <c r="D2">
+        <v>7.5</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2">
+        <v>4.75</v>
+      </c>
+      <c r="G2" t="str">
+        <f>_xlfn.XLOOKUP(F2,$B$14:$B$18,$A$14:$A$18,,-1)</f>
+        <v>SUFICIENTE</v>
+      </c>
+      <c r="I2" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(G2)</f>
+        <v>=BUSCARX(F2,$B$14:$B$18,$A$14:$A$18,,-1)</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>8</v>
+      </c>
+      <c r="D3">
+        <v>7.5</v>
+      </c>
+      <c r="E3">
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>7.625</v>
+      </c>
+      <c r="G3" t="str">
+        <f t="shared" ref="G3:G9" si="0">_xlfn.XLOOKUP(F3,$B$14:$B$18,$A$14:$A$18,,-1)</f>
+        <v>NOTABLE</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4">
+        <v>10</v>
+      </c>
+      <c r="C4">
+        <v>8</v>
+      </c>
+      <c r="D4">
+        <v>6.5</v>
+      </c>
+      <c r="E4">
+        <v>9.5</v>
+      </c>
+      <c r="F4">
+        <v>8.5</v>
+      </c>
+      <c r="G4" t="str">
+        <f t="shared" si="0"/>
+        <v>SOBRESALIENTE</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5">
+        <v>1.5</v>
+      </c>
+      <c r="C5">
+        <v>2.5</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>6</v>
+      </c>
+      <c r="F5">
+        <v>3.25</v>
+      </c>
+      <c r="G5" t="str">
+        <f t="shared" si="0"/>
+        <v>INSUFICIENTE</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6">
+        <v>8.5</v>
+      </c>
+      <c r="C6">
+        <v>5.5</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+      <c r="F6">
+        <v>6.75</v>
+      </c>
+      <c r="G6" t="str">
+        <f t="shared" si="0"/>
+        <v>NOTABLE</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1.75</v>
+      </c>
+      <c r="G7" t="str">
+        <f t="shared" si="0"/>
+        <v>MUY DEFICIENTE</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>6</v>
+      </c>
+      <c r="D8">
+        <v>8</v>
+      </c>
+      <c r="E8">
+        <v>10</v>
+      </c>
+      <c r="F8">
+        <v>7.25</v>
+      </c>
+      <c r="G8" t="str">
+        <f t="shared" si="0"/>
+        <v>NOTABLE</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9">
+        <v>1.5</v>
+      </c>
+      <c r="C9">
+        <v>2.5</v>
+      </c>
+      <c r="D9">
+        <v>1.5</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1.625</v>
+      </c>
+      <c r="G9" t="str">
+        <f t="shared" si="0"/>
+        <v>MUY DEFICIENTE</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18">
+        <v>8.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BE0C6BB-8FCA-407C-B740-8E7EF7416C53}">
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A1" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" t="str">
+        <f>_xlfn.XLOOKUP(A2,T_CODIGOS[CODIGO],T_CODIGOS[MODELO])</f>
+        <v>MOD-004</v>
+      </c>
+      <c r="C2" t="str">
+        <f>LOOKUP(A2,T_CODIGOS[CODIGO],T_CODIGOS[TALLA])</f>
+        <v>L</v>
+      </c>
+      <c r="E2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" t="str">
+        <f>_xlfn.XLOOKUP(A3,T_CODIGOS[CODIGO],T_CODIGOS[MODELO])</f>
+        <v>MOD-005</v>
+      </c>
+      <c r="C3" t="str">
+        <f>LOOKUP(A3,T_CODIGOS[CODIGO],T_CODIGOS[TALLA])</f>
+        <v>XL</v>
+      </c>
+      <c r="E3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" t="str">
+        <f>_xlfn.XLOOKUP(A4,T_CODIGOS[CODIGO],T_CODIGOS[MODELO])</f>
+        <v>MOD-002</v>
+      </c>
+      <c r="C4" t="str">
+        <f>LOOKUP(A4,T_CODIGOS[CODIGO],T_CODIGOS[TALLA])</f>
+        <v>M</v>
+      </c>
+      <c r="E4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" t="str">
+        <f>_xlfn.XLOOKUP(A5,T_CODIGOS[CODIGO],T_CODIGOS[MODELO])</f>
+        <v>MOD-004</v>
+      </c>
+      <c r="C5" t="str">
+        <f>LOOKUP(A5,T_CODIGOS[CODIGO],T_CODIGOS[TALLA])</f>
+        <v>L</v>
+      </c>
+      <c r="E5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" t="str">
+        <f>_xlfn.XLOOKUP(A6,T_CODIGOS[CODIGO],T_CODIGOS[MODELO])</f>
+        <v>MOD-005</v>
+      </c>
+      <c r="C6" t="str">
+        <f>LOOKUP(A6,T_CODIGOS[CODIGO],T_CODIGOS[TALLA])</f>
+        <v>XL</v>
+      </c>
+      <c r="E6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" t="str">
+        <f>_xlfn.XLOOKUP(A7,T_CODIGOS[CODIGO],T_CODIGOS[MODELO])</f>
+        <v>MOD-002</v>
+      </c>
+      <c r="C7" t="str">
+        <f>LOOKUP(A7,T_CODIGOS[CODIGO],T_CODIGOS[TALLA])</f>
+        <v>M</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" t="str">
+        <f>_xlfn.XLOOKUP(A8,T_CODIGOS[CODIGO],T_CODIGOS[MODELO])</f>
+        <v>MOD-003</v>
+      </c>
+      <c r="C8" t="str">
+        <f>LOOKUP(A8,T_CODIGOS[CODIGO],T_CODIGOS[TALLA])</f>
+        <v>S</v>
+      </c>
+      <c r="D8" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(B2)</f>
+        <v>=BUSCARX(A2,T_CODIGOS[CODIGO],T_CODIGOS[MODELO])</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" t="str">
+        <f>_xlfn.XLOOKUP(A9,T_CODIGOS[CODIGO],T_CODIGOS[MODELO])</f>
+        <v>MOD-004</v>
+      </c>
+      <c r="C9" t="str">
+        <f>LOOKUP(A9,T_CODIGOS[CODIGO],T_CODIGOS[TALLA])</f>
+        <v>L</v>
+      </c>
+      <c r="D9" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(C2)</f>
+        <v>=BUSCAR(A2,T_CODIGOS[CODIGO],T_CODIGOS[TALLA])</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" t="str">
+        <f>_xlfn.XLOOKUP(A10,T_CODIGOS[CODIGO],T_CODIGOS[MODELO])</f>
+        <v>MOD-003</v>
+      </c>
+      <c r="C10" t="str">
+        <f>LOOKUP(A10,T_CODIGOS[CODIGO],T_CODIGOS[TALLA])</f>
+        <v>S</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" t="str">
+        <f>_xlfn.XLOOKUP(A11,T_CODIGOS[CODIGO],T_CODIGOS[MODELO])</f>
+        <v>MOD-004</v>
+      </c>
+      <c r="C11" t="str">
+        <f>LOOKUP(A11,T_CODIGOS[CODIGO],T_CODIGOS[TALLA])</f>
+        <v>L</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" t="str">
+        <f>_xlfn.XLOOKUP(A12,T_CODIGOS[CODIGO],T_CODIGOS[MODELO])</f>
+        <v>MOD-005</v>
+      </c>
+      <c r="C12" t="str">
+        <f>LOOKUP(A12,T_CODIGOS[CODIGO],T_CODIGOS[TALLA])</f>
+        <v>XL</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" t="str">
+        <f>_xlfn.XLOOKUP(A13,T_CODIGOS[CODIGO],T_CODIGOS[MODELO])</f>
+        <v>MOD-001</v>
+      </c>
+      <c r="C13" t="str">
+        <f>LOOKUP(A13,T_CODIGOS[CODIGO],T_CODIGOS[TALLA])</f>
+        <v>XL</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" t="str">
+        <f>_xlfn.XLOOKUP(A14,T_CODIGOS[CODIGO],T_CODIGOS[MODELO])</f>
+        <v>MOD-002</v>
+      </c>
+      <c r="C14" t="str">
+        <f>LOOKUP(A14,T_CODIGOS[CODIGO],T_CODIGOS[TALLA])</f>
+        <v>M</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" t="str">
+        <f>_xlfn.XLOOKUP(A15,T_CODIGOS[CODIGO],T_CODIGOS[MODELO])</f>
+        <v>MOD-003</v>
+      </c>
+      <c r="C15" t="str">
+        <f>LOOKUP(A15,T_CODIGOS[CODIGO],T_CODIGOS[TALLA])</f>
+        <v>S</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>